--- a/docs/cadrage/J1/equipe-11-story-map-v1.0.xlsx
+++ b/docs/cadrage/J1/equipe-11-story-map-v1.0.xlsx
@@ -598,7 +598,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
